--- a/backend/data/templates/Patients_Template.xlsx
+++ b/backend/data/templates/Patients_Template.xlsx
@@ -14,6 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="3" r:id="rId1"/>
+    <sheet name="Legend" sheetId="4" r:id="rIdLegend1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,8 +82,68 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,8 +156,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4FC4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4FC4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,17 +189,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -448,6 +597,181 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/legend.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF5B4FC4"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patients — how to fill in this template</t>
+        </is>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• This sheet is documentation only: it is ignored by the import. You can keep it in the file you upload.</t>
+        </is>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Only the columns patient_id and mail are accepted; do not add other columns.</t>
+        </is>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• One row per patient. The upload only creates new patients: existing ones are never modified.</t>
+        </is>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• All or nothing: if any row has an error, no patient is imported. Fix the errors and upload the whole file again.</t>
+        </is>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet "Patients"</t>
+        </is>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to enter</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patients</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identifier of the participant, max 255 characters.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Must be unique within the questionnaire and within the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="33" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patients</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mail</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-mail address (e.g. name@example.com), max 255 characters.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needed to send the invitation. Must be unique within the questionnaire and within the file; saved in lowercase.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887AD610-BD72-40CA-BE06-810C12CDB20B}">
   <dimension ref="A1:B2"/>
